--- a/outputs/ingestion_report.xlsx
+++ b/outputs/ingestion_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="4">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="5">
@@ -666,40 +666,40 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4.84</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAPER_agronomy_15_00961_v2</t>
+          <t>PAPER_27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>agronomy-15-00961-v2.pdf</t>
+          <t>27.pdf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Impact of Organic Amendments on Black Wheat Yield, Grain</t>
+          <t>Journal of the Science of Food and Agriculture</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Black Wheat, Chickpea, Cotton, Cowpea, Maize, Oat, Rice, Sorghum, Soybean, Wheat</t>
+          <t>Barley, Black Wheat, Cabbage, Chickpea, Potato, Rice, Wheat</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.3390/agronomy15040961</t>
+          <t>10.1002/jsfa.2866</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>11224</v>
+        <v>8218</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -713,40 +713,40 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAPER_Bedada_2014</t>
+          <t>PAPER_28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedada 2014.pdf</t>
+          <t>28.pdf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Agriculture,  Ecosystems  and  Environment  195  (2014)  193–201</t>
+          <t>Europ.  J.  Agronomy  51 (2013) 71–  80</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Barley, Chickpea, Maize, Potato, Rice, Sorghum, Wheat</t>
+          <t>Barley, Chickpea, Oat, Potato, Rice, Wheat</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.1016/j.agee.2014.06.017</t>
+          <t>10.1016/j.eja.2013.06.003</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>8931</v>
+        <v>10103</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -760,40 +760,40 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>2.39</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAPER_Behera_2009</t>
+          <t>PAPER_29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Behera 2009.pdf</t>
+          <t>29.pdf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Agricultural Water Management 96 (2009) 1532–1540</t>
+          <t>Zinc use efficiency is enhanced in</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chickpea, Cotton, Groundnut, Maize, Rice, Wheat</t>
+          <t>Barley, Black Wheat, Chickpea, Groundnut, Maize, Oat, Rice, Wheat</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.1016/j.agwat.2009.06.016</t>
+          <t>10.1038/s41598-018-25247-5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>7592</v>
+        <v>6240</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -807,40 +807,40 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAPER_Bell_pepper</t>
+          <t>PAPER_30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bell pepper.pdf</t>
+          <t>30.pdf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASIAN JOURNAL OF AGRICULTURE</t>
+          <t>Plant Pathology (2001) 50, 190–205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bell Pepper, Black Wheat, Chilli, Maize, Oat, Spinach, Wheat</t>
+          <t>Barley, Chickpea, Cotton, Oat, Potato, Wheat</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.13057/asianjagric/g080103</t>
+          <t>10.1046/j.1365-3059.2001.00545.x</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>5182</v>
+        <v>12042</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -854,40 +854,40 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAPER_Black_wheat</t>
+          <t>PAPER_31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Black wheat.pdf</t>
+          <t>31.pdf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>doi: 10.2478/cag-2025-0012</t>
+          <t>Plant Soil (2010) 331:413–425</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Black Wheat, Cabbage, Chickpea, Cowpea, Finger Millet, Maize, Pearl Millet, Rice, Tomato, Wheat</t>
+          <t>Black Wheat, Chickpea, Maize, Pearl Millet, Soybean, Tomato, Wheat</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.2478/cag-2025-0012</t>
+          <t>10.1007/s11104-009-0262-0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>6671</v>
+        <v>9535</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -901,40 +901,40 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAPER_Cai_2006</t>
+          <t>PAPER_32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cai 2006.pdf</t>
+          <t>32.pdf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Geoderma 136 (2006) 708 – 715</t>
+          <t>Plant and Soil (2006) 284: 73–84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Barley, Chickpea, Cotton, Cowpea, Maize, Rice, Soybean, Sugarcane, Wheat</t>
+          <t>Black Wheat, Chickpea, Maize, Rice, Wheat</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.1016/j.geoderma.2006.05.008</t>
+          <t>10.1007/s11104-006-0030-3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>5758</v>
+        <v>6702</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -948,36 +948,40 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAPER_Carrot</t>
+          <t>PAPER_agronomy_15_00961_v2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carrot.pdf</t>
+          <t>agronomy-15-00961-v2.pdf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Biological Forum – An International Journal             16(3): 175-180(2024)</t>
+          <t>Impact of Organic Amendments on Black Wheat Yield, Grain</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Black Wheat, Carrot, Cowpea, Maize, Oat, Onion, Potato, Spinach, Wheat</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Black Wheat, Chickpea, Cotton, Cowpea, Maize, Oat, Rice, Sorghum, Soybean, Wheat</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10.3390/agronomy15040961</t>
+        </is>
+      </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>5077</v>
+        <v>11224</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -991,91 +995,87 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAPER_Cowpea_paper_publish</t>
+          <t>PAPER_Bedada_2014</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cowpea paper publish.pdf</t>
+          <t>Bedada 2014.pdf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASIAN JOURNAL OF AGRICULTURE</t>
+          <t>Agriculture,  Ecosystems  and  Environment  195  (2014)  193–201</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bell Pepper, Carrot, Chickpea, Cowpea, Groundnut, Maize, Oat, Potato, Rice, Spinach, Tomato, Wheat</t>
+          <t>Barley, Chickpea, Maize, Potato, Rice, Sorghum, Wheat</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10.13057/asianjagric/g080105</t>
+          <t>10.1016/j.agee.2014.06.017</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>5757</v>
+        <v>8931</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>New</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>PAPER_Bell_pepper</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>1.78</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAPER_fpls_12_748523</t>
+          <t>PAPER_Behera_2009</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fpls-12-748523.pdf</t>
+          <t>Behera 2009.pdf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>published: 18 October 2021</t>
+          <t>Agricultural Water Management 96 (2009) 1532–1540</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Black Wheat, Chickpea, Groundnut, Maize, Potato, Rice, Soybean, Wheat</t>
+          <t>Chickpea, Cotton, Groundnut, Maize, Rice, Wheat</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10.3389/fpls.2021.748523</t>
+          <t>10.1016/j.agwat.2009.06.016</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>11900</v>
+        <v>7592</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1089,40 +1089,40 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>2.34</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAPER_fpls_16_1521113</t>
+          <t>PAPER_Bell_pepper</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fpls-16-1521113.pdf</t>
+          <t>Bell pepper.pdf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>University of Florida, United States</t>
+          <t>ASIAN JOURNAL OF AGRICULTURE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Black Wheat, Cabbage, Carrot, Chickpea, Groundnut, Maize, Potato, Rice, Soybean, Tomato, Wheat</t>
+          <t>Bell Pepper, Black Wheat, Chilli, Maize, Oat, Spinach, Wheat</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10.3389/fpls.2025.1521113</t>
+          <t>10.13057/asianjagric/g080103</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>11956</v>
+        <v>5182</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1136,40 +1136,40 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAPER_Gardner_2009</t>
+          <t>PAPER_Black_wheat</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gardner 2009.pdf</t>
+          <t>Black wheat.pdf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ecological Applications, 19(8), 2009, pp. 2167–2184</t>
+          <t>doi: 10.2478/cag-2025-0012</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Barley, Black Wheat, Chickpea, Cotton, Maize, Onion, Potato, Rice, Soybean, Wheat</t>
+          <t>Black Wheat, Cabbage, Chickpea, Cowpea, Finger Millet, Maize, Pearl Millet, Rice, Tomato, Wheat</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.1890/08-1122.1</t>
+          <t>10.2478/cag-2025-0012</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>13806</v>
+        <v>6671</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1183,40 +1183,40 @@
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAPER_Katterer_2011</t>
+          <t>PAPER_Cai_2006</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Katterer 2011.pdf</t>
+          <t>Cai 2006.pdf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Agriculture, Ecosystems and Environment 141 (2011) 184–192</t>
+          <t>Geoderma 136 (2006) 708 – 715</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Barley, Chickpea, Maize, Mustard, Oat, Wheat</t>
+          <t>Barley, Chickpea, Cotton, Cowpea, Maize, Rice, Soybean, Sugarcane, Wheat</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.1016/j.agee.2011.02.029</t>
+          <t>10.1016/j.geoderma.2006.05.008</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>10095</v>
+        <v>5758</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1230,40 +1230,36 @@
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>1.36</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAPER_Land_Degrad_Dev___2021___Yadav___Sustain</t>
+          <t>PAPER_Carrot</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Land Degrad Dev - 2021 - Yadav - Sustaining the properties of black soil in Central India through crop residue management.pdf</t>
+          <t>Carrot.pdf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Received: 8 January 2020</t>
+          <t>Biological Forum – An International Journal             16(3): 175-180(2024)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Black Wheat, Chickpea, Maize, Potato, Rice, Soybean, Wheat</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>10.1002/ldr.3891</t>
-        </is>
-      </c>
+          <t>Black Wheat, Carrot, Cowpea, Maize, Oat, Onion, Potato, Spinach, Wheat</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>11387</v>
+        <v>5077</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1277,87 +1273,91 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAPER_Maltas_2015</t>
+          <t>PAPER_Cowpea_paper_publish</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maltas 2015.pdf</t>
+          <t>Cowpea paper publish.pdf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Soil  &amp;  Tillage  Research  126  (2013)  11–18</t>
+          <t>ASIAN JOURNAL OF AGRICULTURE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Barley, Chickpea, Cotton, Maize, Oat, Rice, Sorghum, Soybean, Wheat</t>
+          <t>Bell Pepper, Carrot, Chickpea, Cowpea, Groundnut, Maize, Oat, Potato, Rice, Spinach, Tomato, Wheat</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10.1016/j.still.2012.07.012</t>
+          <t>10.13057/asianjagric/g080105</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>8408</v>
+        <v>5757</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Duplicate</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PAPER_Bell_pepper</t>
+        </is>
+      </c>
       <c r="K19" t="n">
-        <v>2.43</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAPER_Maltas_2018</t>
+          <t>PAPER_fpls_12_748523</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maltas 2018.pdf</t>
+          <t>fpls-12-748523.pdf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Received: 31 May 2017</t>
+          <t>published: 18 October 2021</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Barley, Chickpea, Maize, Mustard, Oat, Wheat</t>
+          <t>Black Wheat, Chickpea, Groundnut, Maize, Potato, Rice, Soybean, Wheat</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.1002/ldr.2913</t>
+          <t>10.3389/fpls.2021.748523</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>10297</v>
+        <v>11900</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1371,40 +1371,40 @@
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAPER_s41477_021_01001_0</t>
+          <t>PAPER_fpls_16_1521113</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>s41477-021-01001-0.pdf</t>
+          <t>fpls-16-1521113.pdf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Explainable machine learning models of</t>
+          <t>University of Florida, United States</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Chickpea, Cotton, Maize, Oat, Wheat</t>
+          <t>Black Wheat, Cabbage, Carrot, Chickpea, Groundnut, Maize, Potato, Rice, Soybean, Tomato, Wheat</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10.1038/s41477-021-01001-0</t>
+          <t>10.3389/fpls.2025.1521113</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>9529</v>
+        <v>11956</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1418,40 +1418,40 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>9.65</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAPER_s41598_017_03539_6</t>
+          <t>PAPER_Gardner_2009</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>s41598-017-03539-6.pdf</t>
+          <t>Gardner 2009.pdf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Received: 22 February 2017</t>
+          <t>Ecological Applications, 19(8), 2009, pp. 2167–2184</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Chickpea, Maize, Potato, Rice, Soybean, Sugarcane, Wheat</t>
+          <t>Barley, Black Wheat, Chickpea, Cotton, Maize, Onion, Potato, Rice, Soybean, Wheat</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10.1038/s41598-017-03539-6</t>
+          <t>10.1890/08-1122.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>6930</v>
+        <v>13806</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1465,40 +1465,40 @@
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PAPER_s42106_025_00391_x</t>
+          <t>PAPER_Katterer_2011</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>s42106-025-00391-x.pdf</t>
+          <t>Katterer 2011.pdf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>International Journal of Plant Production (2026) 20:3</t>
+          <t>Agriculture, Ecosystems and Environment 141 (2011) 184–192</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Black Wheat, Chickpea, Groundnut, Maize, Oat, Rice, Wheat</t>
+          <t>Barley, Chickpea, Maize, Mustard, Oat, Wheat</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10.1007/s42106-025-00391-x</t>
+          <t>10.1016/j.agee.2011.02.029</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>11623</v>
+        <v>10095</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1512,40 +1512,40 @@
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>2.09</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PAPER_Spinach</t>
+          <t>PAPER_Land_Degrad_Dev___2021___Yadav___Sustain</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spinach.pdf</t>
+          <t>Land Degrad Dev - 2021 - Yadav - Sustaining the properties of black soil in Central India through crop residue management.pdf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(Published by Research Trend, Website: www.agribioinnovations.com)</t>
+          <t>Received: 8 January 2020</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Barley, Brinjal, Carrot, Chickpea, Cotton, Maize, Rice, Sorghum, Spinach, Tomato, Wheat</t>
+          <t>Black Wheat, Chickpea, Maize, Potato, Rice, Soybean, Wheat</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10.65041/AgriBioInnovations.2026.3.1.1</t>
+          <t>10.1002/ldr.3891</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="G24" t="n">
-        <v>4794</v>
+        <v>11387</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1559,40 +1559,40 @@
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>1.38</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAPER_Wang_2015</t>
+          <t>PAPER_Maltas_2015</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wang 2015.pdf</t>
+          <t>Maltas 2015.pdf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>J Soils Sediments (2015) 15:260–270</t>
+          <t>Soil  &amp;  Tillage  Research  126  (2013)  11–18</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Barley, Black Wheat, Chickpea, Maize, Sorghum, Soybean, Wheat</t>
+          <t>Barley, Chickpea, Cotton, Maize, Oat, Rice, Sorghum, Soybean, Wheat</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10.1007/s11368-014-0989-y</t>
+          <t>10.1016/j.still.2012.07.012</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G25" t="n">
-        <v>7929</v>
+        <v>8408</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1606,7 +1606,289 @@
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>1.37</v>
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PAPER_Maltas_2018</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Maltas 2018.pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Received: 31 May 2017</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Barley, Chickpea, Maize, Mustard, Oat, Wheat</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>10.1002/ldr.2913</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>52</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10297</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PAPER_s41477_021_01001_0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>s41477-021-01001-0.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Explainable machine learning models of</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Chickpea, Cotton, Maize, Oat, Wheat</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10.1038/s41477-021-01001-0</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>38</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9529</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PAPER_s41598_017_03539_6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>s41598-017-03539-6.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Received: 22 February 2017</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Chickpea, Maize, Potato, Rice, Soybean, Sugarcane, Wheat</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-017-03539-6</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>15</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6930</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PAPER_s42106_025_00391_x</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>s42106-025-00391-x.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>International Journal of Plant Production (2026) 20:3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Black Wheat, Chickpea, Groundnut, Maize, Oat, Rice, Wheat</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10.1007/s42106-025-00391-x</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>34</v>
+      </c>
+      <c r="G29" t="n">
+        <v>11623</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PAPER_Spinach</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Spinach.pdf</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>(Published by Research Trend, Website: www.agribioinnovations.com)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Barley, Brinjal, Carrot, Chickpea, Cotton, Maize, Rice, Sorghum, Spinach, Tomato, Wheat</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10.65041/AgriBioInnovations.2026.3.1.1</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4794</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PAPER_Wang_2015</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Wang 2015.pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>J Soils Sediments (2015) 15:260–270</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Barley, Black Wheat, Chickpea, Maize, Sorghum, Soybean, Wheat</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10.1007/s11368-014-0989-y</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7929</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ingestion_report.xlsx
+++ b/outputs/ingestion_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,38 +476,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAPER_1_s2_0_S0016706120325842_main</t>
+          <t>PAPER_1_s2_0_S0016706106001686_main</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1-s2.0-S0016706120325842-main.pdf</t>
+          <t>1-s2.0-S0016706106001686-main.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Contents lists available at ScienceDirect</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Chickpea, Maize, Soybean, Wheat</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10.1016/j.geoderma.2020.114829</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -517,44 +509,36 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAPER_1_s2_0_S0048969721016284_main</t>
+          <t>PAPER_1_s2_0_S0016706120325842_main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1-s2.0-S0048969721016284-main.pdf</t>
+          <t>1-s2.0-S0016706120325842-main.pdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Science of the Total Environment 780 (2021) 146560</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Barley, Black Wheat, Chickpea, Cotton, Maize, Oat, Rice, Soybean, Spinach, Wheat</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>10.1016/j.scitotenv.2021.146560</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>11376</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -564,146 +548,114 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAPER_1_s2_0_S0167880922002316_main</t>
+          <t>PAPER_1_s2_0_S0016706123001490_main</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1-s2.0-S0167880922002316-main.pdf</t>
+          <t>1-s2.0-S0016706123001490-main.pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contents lists available at ScienceDirect</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chickpea, Cotton, Maize, Rice, Soybean, Tomato, Wheat</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>10.1016/j.agee.2022.108082</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>10065</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>PAPER_1_s2_0_S0016706120325842_main</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAPER_1_s2_0_S0301479721013128_main</t>
+          <t>PAPER_1_s2_0_S0038071716300761_main</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1-s2.0-S0301479721013128-main.pdf</t>
+          <t>1-s2.0-S0038071716300761-main.pdf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contents lists available at ScienceDirect</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Barley, Black Wheat, Maize, Rice, Tomato, Wheat</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10.1016/j.jenvman.2021.113250</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>9010</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>PAPER_1_s2_0_S0016706120325842_main</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAPER_27</t>
+          <t>PAPER_1_s2_0_S0038071719300793_main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.pdf</t>
+          <t>1-s2.0-S0038071719300793-main.pdf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Journal of the Science of Food and Agriculture</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Barley, Black Wheat, Cabbage, Chickpea, Potato, Rice, Wheat</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10.1002/jsfa.2866</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>8218</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -713,44 +665,36 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAPER_28</t>
+          <t>PAPER_1_s2_0_S0045653522010621_main</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28.pdf</t>
+          <t>1-s2.0-S0045653522010621-main.pdf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Europ.  J.  Agronomy  51 (2013) 71–  80</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Barley, Chickpea, Oat, Potato, Rice, Wheat</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10.1016/j.eja.2013.06.003</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>10103</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -760,44 +704,36 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAPER_29</t>
+          <t>PAPER_1_s2_0_S0048969720328382_main</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29.pdf</t>
+          <t>1-s2.0-S0048969720328382-main.pdf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zinc use efficiency is enhanced in</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Barley, Black Wheat, Chickpea, Groundnut, Maize, Oat, Rice, Wheat</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>10.1038/s41598-018-25247-5</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6240</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -807,44 +743,36 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAPER_30</t>
+          <t>PAPER_1_s2_0_S0048969721016284_main</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.pdf</t>
+          <t>1-s2.0-S0048969721016284-main.pdf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plant Pathology (2001) 50, 190–205</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Barley, Chickpea, Cotton, Oat, Potato, Wheat</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>10.1046/j.1365-3059.2001.00545.x</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>12042</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -854,44 +782,36 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAPER_31</t>
+          <t>PAPER_1_s2_0_S004896972105542X_main</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31.pdf</t>
+          <t>1-s2.0-S004896972105542X-main.pdf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plant Soil (2010) 331:413–425</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Black Wheat, Chickpea, Maize, Pearl Millet, Soybean, Tomato, Wheat</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>10.1007/s11104-009-0262-0</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>9535</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -901,44 +821,36 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAPER_32</t>
+          <t>PAPER_1_s2_0_S0167198712001547_main</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32.pdf</t>
+          <t>1-s2.0-S0167198712001547-main.pdf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plant and Soil (2006) 284: 73–84</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Black Wheat, Chickpea, Maize, Rice, Wheat</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>10.1007/s11104-006-0030-3</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>6702</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -948,44 +860,36 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAPER_agronomy_15_00961_v2</t>
+          <t>PAPER_1_s2_0_S0167198718300722_main</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>agronomy-15-00961-v2.pdf</t>
+          <t>1-s2.0-S0167198718300722-main.pdf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Impact of Organic Amendments on Black Wheat Yield, Grain</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Black Wheat, Chickpea, Cotton, Cowpea, Maize, Oat, Rice, Sorghum, Soybean, Wheat</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>10.3390/agronomy15040961</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>11224</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -995,44 +899,36 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAPER_Bedada_2014</t>
+          <t>PAPER_1_s2_0_S0167198720305808_main</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedada 2014.pdf</t>
+          <t>1-s2.0-S0167198720305808-main.pdf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Agriculture,  Ecosystems  and  Environment  195  (2014)  193–201</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Barley, Chickpea, Maize, Potato, Rice, Sorghum, Wheat</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>10.1016/j.agee.2014.06.017</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>8931</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1042,44 +938,36 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAPER_Behera_2009</t>
+          <t>PAPER_1_s2_0_S0167880911000818_main</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Behera 2009.pdf</t>
+          <t>1-s2.0-S0167880911000818-main.pdf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Agricultural Water Management 96 (2009) 1532–1540</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Chickpea, Cotton, Groundnut, Maize, Rice, Wheat</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>10.1016/j.agwat.2009.06.016</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7592</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1089,44 +977,36 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAPER_Bell_pepper</t>
+          <t>PAPER_1_s2_0_S0167880914003375_main</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bell pepper.pdf</t>
+          <t>1-s2.0-S0167880914003375-main.pdf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ASIAN JOURNAL OF AGRICULTURE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bell Pepper, Black Wheat, Chilli, Maize, Oat, Spinach, Wheat</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>10.13057/asianjagric/g080103</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>5182</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1136,44 +1016,36 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAPER_Black_wheat</t>
+          <t>PAPER_1_s2_0_S0167880916301980_main</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Black wheat.pdf</t>
+          <t>1-s2.0-S0167880916301980-main.pdf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>doi: 10.2478/cag-2025-0012</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Black Wheat, Cabbage, Chickpea, Cowpea, Finger Millet, Maize, Pearl Millet, Rice, Tomato, Wheat</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>10.2478/cag-2025-0012</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>6671</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1183,44 +1055,36 @@
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAPER_Cai_2006</t>
+          <t>PAPER_1_s2_0_S0167880922002316_main</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cai 2006.pdf</t>
+          <t>1-s2.0-S0167880922002316-main.pdf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Geoderma 136 (2006) 708 – 715</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Barley, Chickpea, Cotton, Cowpea, Maize, Rice, Soybean, Sugarcane, Wheat</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>10.1016/j.geoderma.2006.05.008</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>5758</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1230,40 +1094,36 @@
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAPER_Carrot</t>
+          <t>PAPER_1_s2_0_S0269749121013233_main</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carrot.pdf</t>
+          <t>1-s2.0-S0269749121013233-main.pdf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Biological Forum – An International Journal             16(3): 175-180(2024)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Black Wheat, Carrot, Cowpea, Maize, Oat, Onion, Potato, Spinach, Wheat</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>5077</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1273,95 +1133,75 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAPER_Cowpea_paper_publish</t>
+          <t>PAPER_1_s2_0_S0301479721013128_main</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cowpea paper publish.pdf</t>
+          <t>1-s2.0-S0301479721013128-main.pdf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ASIAN JOURNAL OF AGRICULTURE</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bell Pepper, Carrot, Chickpea, Cowpea, Groundnut, Maize, Oat, Potato, Rice, Spinach, Tomato, Wheat</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>10.13057/asianjagric/g080105</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>5757</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>PAPER_Bell_pepper</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAPER_fpls_12_748523</t>
+          <t>PAPER_1_s2_0_S0304387821001450_main</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fpls-12-748523.pdf</t>
+          <t>1-s2.0-S0304387821001450-main.pdf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>published: 18 October 2021</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Black Wheat, Chickpea, Groundnut, Maize, Potato, Rice, Soybean, Wheat</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>10.3389/fpls.2021.748523</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>11900</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1371,44 +1211,36 @@
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAPER_fpls_16_1521113</t>
+          <t>PAPER_1_s2_0_S0378377409001681_main</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fpls-16-1521113.pdf</t>
+          <t>1-s2.0-S0378377409001681-main.pdf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>University of Florida, United States</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Black Wheat, Cabbage, Carrot, Chickpea, Groundnut, Maize, Potato, Rice, Soybean, Tomato, Wheat</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>10.3389/fpls.2025.1521113</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>11956</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1418,44 +1250,36 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAPER_Gardner_2009</t>
+          <t>PAPER_1_s2_0_S0378377420321028_main</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gardner 2009.pdf</t>
+          <t>1-s2.0-S0378377420321028-main.pdf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ecological Applications, 19(8), 2009, pp. 2167–2184</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Barley, Black Wheat, Chickpea, Cotton, Maize, Onion, Potato, Rice, Soybean, Wheat</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>10.1890/08-1122.1</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>13806</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1465,44 +1289,36 @@
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PAPER_Katterer_2011</t>
+          <t>PAPER_1_s2_0_S0378377421004911_main</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Katterer 2011.pdf</t>
+          <t>1-s2.0-S0378377421004911-main.pdf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agriculture, Ecosystems and Environment 141 (2011) 184–192</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Barley, Chickpea, Maize, Mustard, Oat, Wheat</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>10.1016/j.agee.2011.02.029</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>10095</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1512,44 +1328,36 @@
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PAPER_Land_Degrad_Dev___2021___Yadav___Sustain</t>
+          <t>PAPER_1_s2_0_S0378377423001919_main</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Land Degrad Dev - 2021 - Yadav - Sustaining the properties of black soil in Central India through crop residue management.pdf</t>
+          <t>1-s2.0-S0378377423001919-main.pdf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Received: 8 January 2020</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Black Wheat, Chickpea, Maize, Potato, Rice, Soybean, Wheat</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>10.1002/ldr.3891</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>11387</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1559,44 +1367,36 @@
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAPER_Maltas_2015</t>
+          <t>PAPER_1_s2_0_S0378429017309723_main</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maltas 2015.pdf</t>
+          <t>1-s2.0-S0378429017309723-main.pdf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Soil  &amp;  Tillage  Research  126  (2013)  11–18</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Barley, Chickpea, Cotton, Maize, Oat, Rice, Sorghum, Soybean, Wheat</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>10.1016/j.still.2012.07.012</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>8408</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1606,44 +1406,36 @@
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAPER_Maltas_2018</t>
+          <t>PAPER_1_s2_0_S0925857415001810_main</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maltas 2018.pdf</t>
+          <t>1-s2.0-S0925857415001810-main.pdf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Received: 31 May 2017</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Barley, Chickpea, Maize, Mustard, Oat, Wheat</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>10.1002/ldr.2913</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>10297</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1653,44 +1445,36 @@
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAPER_s41477_021_01001_0</t>
+          <t>PAPER_1_s2_0_S0929139316302864_main</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>s41477-021-01001-0.pdf</t>
+          <t>1-s2.0-S0929139316302864-main.pdf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Explainable machine learning models of</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Chickpea, Cotton, Maize, Oat, Wheat</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>10.1038/s41477-021-01001-0</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>9529</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1700,44 +1484,36 @@
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAPER_s41598_017_03539_6</t>
+          <t>PAPER_1_s2_0_S0929139321000974_main</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>s41598-017-03539-6.pdf</t>
+          <t>1-s2.0-S0929139321000974-main.pdf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Received: 22 February 2017</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Chickpea, Maize, Potato, Rice, Soybean, Sugarcane, Wheat</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>10.1038/s41598-017-03539-6</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>6930</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1747,44 +1523,36 @@
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PAPER_s42106_025_00391_x</t>
+          <t>PAPER_1_s2_0_S1161030122001897_main</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>s42106-025-00391-x.pdf</t>
+          <t>1-s2.0-S1161030122001897-main.pdf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>International Journal of Plant Production (2026) 20:3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Black Wheat, Chickpea, Groundnut, Maize, Oat, Rice, Wheat</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>10.1007/s42106-025-00391-x</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>11623</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1794,44 +1562,36 @@
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PAPER_Spinach</t>
+          <t>PAPER_10july22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spinach.pdf</t>
+          <t>10july22.pdf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(Published by Research Trend, Website: www.agribioinnovations.com)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Barley, Brinjal, Carrot, Chickpea, Cotton, Maize, Rice, Sorghum, Spinach, Tomato, Wheat</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>10.65041/AgriBioInnovations.2026.3.1.1</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>4794</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1841,44 +1601,36 @@
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PAPER_Wang_2015</t>
+          <t>PAPER_14july22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wang 2015.pdf</t>
+          <t>14july22.pdf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>J Soils Sediments (2015) 15:260–270</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Barley, Black Wheat, Chickpea, Maize, Sorghum, Soybean, Wheat</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>10.1007/s11368-014-0989-y</t>
-        </is>
-      </c>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>7929</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Previously Processed</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1888,7 +1640,2386 @@
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
-        <v>1.39</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PAPER_15july22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>15july22.pdf</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PAPER_17july22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>17july22.pdf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PAPER_18july22</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>18july22.pdf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PAPER_19july22</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>19july22.pdf</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PAPER_1July20</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1July20.pdf</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PAPER_1july22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1july22.pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PAPER_20july22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20july22.pdf</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PAPER_24july22</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>24july22.pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PAPER_25july22</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>25july22.pdf</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PAPER_26july22</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>26july22.pdf</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PAPER_27july22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>27july22.pdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PAPER_28july22</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>28july22.pdf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PAPER_29july22</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>29july22.pdf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PAPER_2July20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2July20.pdf</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PAPER_2july22</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2july22.pdf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PAPER_30july22</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>30july22.pdf</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PAPER_31july22</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>31july22.pdf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PAPER_32july22</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>32july22.pdf</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PAPER_33july22</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>33july22.pdf</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PAPER_34july22</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>34july22.pdf</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PAPER_35july22</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>35july22.pdf</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PAPER_36july22</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>36july22.pdf</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PAPER_37july22</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>37july22.pdf</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PAPER_38july22</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>38july22.pdf</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PAPER_39july22</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>39july22.pdf</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PAPER_3july20</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>3july20.pdf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PAPER_3july22</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>3july22.pdf</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PAPER_4july20</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4july20.pdf</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PAPER_4july22</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4july22.pdf</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PAPER_5july20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5july20.pdf</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PAPER_5july22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5july22.pdf</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PAPER_6july20</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>6july20.pdf</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PAPER_6july22</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>6july22.pdf</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PAPER_7july20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7july20.pdf</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PAPER_7july22</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>7july22.pdf</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PAPER_8july22</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>8july22.pdf</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PAPER_9july22</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>9july22.pdf</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PAPER_agronomy_09_00776_v2</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>agronomy-09-00776-v2.pdf</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PAPER_agronomy_11_00636_v2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>agronomy-11-00636-v2.pdf</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PAPER_agronomy_15_00961_v2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>agronomy-15-00961-v2.pdf</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PAPER_Bell_pepper</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Bell pepper.pdf</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PAPER_Black_wheat</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Black wheat.pdf</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PAPER_Carrot</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Carrot.pdf</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PAPER_Cowpea_paper_publish</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Cowpea paper publish.pdf</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PAPER_fagro_04_848621</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>fagro-04-848621.pdf</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PAPER_fpls_12_748523</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>fpls-12-748523.pdf</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PAPER_fpls_16_1521113</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>fpls-16-1521113.pdf</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PAPER_J_Sci_Food_Agric___2020___Singh___Agricu</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>J Sci Food Agric - 2020 - Singh - Agricultural practices modulate the bacterial communities  and nitrogen cycling bacterial.pdf</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PAPER_Land_Degrad_Dev___2018___Maltas___The_ef</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Land Degrad Dev - 2018 - Maltas - The effects of organic and mineral fertilizers on carbon sequestration  soil properties .pdf</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PAPER_Land_Degrad_Dev___2021___Yadav___Sustain</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Land Degrad Dev - 2021 - Yadav - Sustaining the properties of black soil in Central India through crop residue management.pdf</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PAPER_s11368_014_0989_y</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>s11368-014-0989-y.pdf</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PAPER_s11368_018_1933_3</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>s11368-018-1933-3.pdf</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PAPER_s13593_023_00923_7</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>s13593-023-00923-7.pdf</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PAPER_s41477_021_01001_0</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>s41477-021-01001-0.pdf</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PAPER_s41598_017_03539_6</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>s41598-017-03539-6.pdf</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PAPER_s41893_020_0569_7</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>s41893-020-0569-7.pdf</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PAPER_s42106_025_00391_x</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>s42106-025-00391-x.pdf</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PAPER_s42773_024_00332_3</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>s42773-024-00332-3.pdf</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PAPER_Soil_Use_and_Management___2019___Ye___Bi</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Soil Use and Management - 2019 - Ye - Biochar effects on crop yields with and without fertilizer  A metaΓÇÉanalysis of field.pdf</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PAPER_Spinach</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Spinach.pdf</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PAPER_sustainability_07_13713</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>sustainability-07-13713.pdf</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>(Previously processed)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Previously Processed</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
